--- a/data/trans_dic/IP2003-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen dientes o muelas empastados</t>
+          <t>Menores que tienen dientes o muelas empastados (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,29; 24,32</t>
+          <t>12,81; 23,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,84; 21,93</t>
+          <t>11,13; 21,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 17,65</t>
+          <t>7,57; 17,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 15,71</t>
+          <t>6,33; 15,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 20,34</t>
+          <t>10,4; 19,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 23,7</t>
+          <t>12,78; 23,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 14,04</t>
+          <t>5,78; 14,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 33,5</t>
+          <t>2,96; 34,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,78; 19,69</t>
+          <t>12,55; 20,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 21,23</t>
+          <t>13,11; 20,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 13,84</t>
+          <t>7,52; 14,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 22,68</t>
+          <t>6,04; 23,53</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,45; 26,9</t>
+          <t>17,02; 26,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,6; 25,13</t>
+          <t>15,71; 24,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 18,18</t>
+          <t>10,2; 18,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 14,07</t>
+          <t>6,44; 13,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,8; 19,64</t>
+          <t>12,01; 19,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 18,33</t>
+          <t>10,54; 18,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 18,85</t>
+          <t>11,02; 18,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,75; 22,5</t>
+          <t>10,77; 21,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,51; 21,37</t>
+          <t>15,41; 21,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,82; 19,81</t>
+          <t>14,15; 20,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 17,59</t>
+          <t>11,59; 17,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 17,07</t>
+          <t>9,63; 16,72</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,15; 26,88</t>
+          <t>15,79; 26,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 19,2</t>
+          <t>10,07; 19,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 16,18</t>
+          <t>8,01; 15,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,11; 59,36</t>
+          <t>20,02; 58,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,9; 20,3</t>
+          <t>10,55; 20,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,38; 18,69</t>
+          <t>9,71; 18,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,34; 18,39</t>
+          <t>9,48; 17,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,67; 24,65</t>
+          <t>12,94; 24,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 21,47</t>
+          <t>14,46; 22,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 17,16</t>
+          <t>11,07; 17,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 15,88</t>
+          <t>9,71; 15,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 43,72</t>
+          <t>18,54; 43,37</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 15,86</t>
+          <t>7,8; 15,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,96; 20,91</t>
+          <t>11,77; 21,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,9; 21,24</t>
+          <t>11,49; 21,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 17,08</t>
+          <t>8,51; 17,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 16,48</t>
+          <t>8,49; 16,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,87</t>
+          <t>5,86; 12,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,64; 17,82</t>
+          <t>9,58; 18,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 15,53</t>
+          <t>7,72; 15,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,89</t>
+          <t>9,18; 14,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 15,47</t>
+          <t>10,04; 15,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,6; 17,89</t>
+          <t>11,64; 18,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 14,68</t>
+          <t>8,95; 15,16</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,19; 19,93</t>
+          <t>15,33; 20,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,38; 19,21</t>
+          <t>14,54; 19,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,24; 15,73</t>
+          <t>11,29; 15,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 28,55</t>
+          <t>12,71; 29,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,22; 16,33</t>
+          <t>12,35; 16,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,44</t>
+          <t>11,25; 15,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 15,14</t>
+          <t>11,14; 15,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,46; 18,73</t>
+          <t>11,39; 18,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,28; 17,45</t>
+          <t>14,33; 17,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,3; 16,49</t>
+          <t>13,37; 16,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,75; 14,83</t>
+          <t>11,82; 14,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,05; 21,88</t>
+          <t>12,91; 21,3</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen dientes o muelas empastados (tasa de respuesta: 99,85%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>23058</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21365</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14530</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11817</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20989</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24946</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13252</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>15885</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>44047</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>46311</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27782</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>27702</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>16524; 30947</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14818; 29132</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9436; 21600</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7280; 17925</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14931; 28449</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>18170; 33411</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8043; 20678</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4045; 47774</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>34208; 54844</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>36097; 56976</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>19845; 37251</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>15221; 59264</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38399</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26707</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17615</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31474</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29790</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>30912</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>37164</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>71474</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>68189</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>57619</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>54779</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>31612; 49424</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>30083; 47816</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19711; 35812</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12038; 25884</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>24609; 40771</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22414; 39455</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>23218; 39532</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>26832; 53177</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>60224; 83948</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>57192; 81065</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>46830; 71148</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>41973; 72892</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>27425</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20635</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16937</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>63290</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21053</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20624</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>21243</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>32596</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>48478</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>41260</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>38181</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>95885</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>20638; 35174</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14571; 28482</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11865; 23605</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37627; 109286</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>14705; 28259</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14782; 28420</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>15211; 28765</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>23778; 44284</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>39051; 59442</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>32858; 51596</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>29969; 48904</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>68894; 161219</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>22822</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30832</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30781</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20326</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24019</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17437</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>19720</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>46841</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>48269</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>56274</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>40046</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>15564; 31779</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22786; 40920</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22121; 40726</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>14135; 29091</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>16740; 32342</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>11493; 24935</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>18260; 34591</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>13730; 27978</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>36421; 58972</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>39149; 61221</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>44606; 69523</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>30793; 52133</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>113305</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>111231</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>88955</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>113048</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>105364</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>210840</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>204028</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>179856</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>218412</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>98898; 129850</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>96409; 127193</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>74365; 103934</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>83378; 192532</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>84568; 112638</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>79135; 109947</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>78067; 107974</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>85121; 138824</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>190643; 232740</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>182712; 225701</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>160639; 202155</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>181128; 298933</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2003-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,81; 23,99</t>
+          <t>12,72; 23,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,13; 21,88</t>
+          <t>11,46; 22,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 17,33</t>
+          <t>7,08; 17,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 15,58</t>
+          <t>6,15; 15,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 19,82</t>
+          <t>10,34; 20,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,78; 23,51</t>
+          <t>12,45; 23,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 14,86</t>
+          <t>5,92; 14,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 34,93</t>
+          <t>2,91; 36,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,55; 20,13</t>
+          <t>13,15; 20,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,11; 20,7</t>
+          <t>13,1; 20,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 14,12</t>
+          <t>7,75; 14,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 23,53</t>
+          <t>5,82; 24,2</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 26,6</t>
+          <t>17,05; 26,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 24,97</t>
+          <t>15,88; 24,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 18,53</t>
+          <t>10,52; 18,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 13,85</t>
+          <t>6,24; 13,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,01; 19,9</t>
+          <t>11,8; 19,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,54; 18,54</t>
+          <t>10,5; 18,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,02; 18,76</t>
+          <t>10,89; 19,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,77; 21,34</t>
+          <t>10,49; 22,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 21,49</t>
+          <t>15,27; 21,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,15; 20,05</t>
+          <t>14,42; 19,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,59; 17,61</t>
+          <t>11,77; 17,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 16,72</t>
+          <t>9,76; 16,72</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,79; 26,91</t>
+          <t>15,58; 27,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 19,69</t>
+          <t>10,33; 19,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 15,93</t>
+          <t>7,95; 16,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,02; 58,14</t>
+          <t>20,11; 57,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 20,28</t>
+          <t>10,96; 19,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 18,66</t>
+          <t>9,41; 18,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,48; 17,93</t>
+          <t>8,98; 17,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,94; 24,11</t>
+          <t>13,22; 24,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,46; 22,01</t>
+          <t>14,35; 22,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,07; 17,38</t>
+          <t>10,95; 17,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 15,85</t>
+          <t>9,49; 15,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,54; 43,37</t>
+          <t>18,35; 42,56</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 15,93</t>
+          <t>7,94; 15,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,77; 21,14</t>
+          <t>11,43; 20,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 21,16</t>
+          <t>12,12; 21,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 17,51</t>
+          <t>8,14; 16,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 16,41</t>
+          <t>8,35; 16,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,7</t>
+          <t>5,73; 12,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 18,14</t>
+          <t>9,5; 17,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 15,73</t>
+          <t>7,61; 16,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,18; 14,87</t>
+          <t>9,07; 14,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 15,71</t>
+          <t>9,76; 15,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 18,14</t>
+          <t>11,8; 18,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 15,16</t>
+          <t>8,73; 15,05</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 20,13</t>
+          <t>15,26; 20,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,54; 19,19</t>
+          <t>14,58; 19,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,78</t>
+          <t>11,23; 15,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,71; 29,35</t>
+          <t>12,97; 29,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,35; 16,45</t>
+          <t>12,25; 16,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,63</t>
+          <t>11,34; 15,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,14; 15,41</t>
+          <t>11,07; 15,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 18,57</t>
+          <t>11,3; 19,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,33; 17,5</t>
+          <t>14,33; 17,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,37; 16,52</t>
+          <t>13,36; 16,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 14,87</t>
+          <t>11,67; 14,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,91; 21,3</t>
+          <t>12,88; 21,61</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16524; 30947</t>
+          <t>16405; 30620</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14818; 29132</t>
+          <t>15257; 29676</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9436; 21600</t>
+          <t>8825; 22106</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7280; 17925</t>
+          <t>7081; 18060</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14931; 28449</t>
+          <t>14845; 28909</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18170; 33411</t>
+          <t>17693; 33936</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8043; 20678</t>
+          <t>8235; 20524</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4045; 47774</t>
+          <t>3978; 49435</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34208; 54844</t>
+          <t>35844; 54991</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36097; 56976</t>
+          <t>36073; 56161</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19845; 37251</t>
+          <t>20453; 37567</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15221; 59264</t>
+          <t>14648; 60932</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31612; 49424</t>
+          <t>31680; 49589</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30083; 47816</t>
+          <t>30421; 47779</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19711; 35812</t>
+          <t>20326; 36287</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12038; 25884</t>
+          <t>11667; 25403</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24609; 40771</t>
+          <t>24173; 40157</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22414; 39455</t>
+          <t>22332; 39644</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23218; 39532</t>
+          <t>22945; 40271</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26832; 53177</t>
+          <t>26129; 55171</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60224; 83948</t>
+          <t>59647; 84289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57192; 81065</t>
+          <t>58277; 80550</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46830; 71148</t>
+          <t>47530; 69935</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41973; 72892</t>
+          <t>42569; 72914</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20638; 35174</t>
+          <t>20364; 35373</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14571; 28482</t>
+          <t>14937; 28795</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11865; 23605</t>
+          <t>11781; 24220</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37627; 109286</t>
+          <t>37811; 107582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14705; 28259</t>
+          <t>15278; 27589</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14782; 28420</t>
+          <t>14332; 27588</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15211; 28765</t>
+          <t>14412; 28819</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23778; 44284</t>
+          <t>24291; 44859</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39051; 59442</t>
+          <t>38746; 59451</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32858; 51596</t>
+          <t>32529; 50846</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29969; 48904</t>
+          <t>29276; 48248</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68894; 161219</t>
+          <t>68217; 158177</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15564; 31779</t>
+          <t>15851; 30957</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22786; 40920</t>
+          <t>22119; 39607</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22121; 40726</t>
+          <t>23337; 41244</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14135; 29091</t>
+          <t>13519; 28065</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16740; 32342</t>
+          <t>16454; 32431</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11493; 24935</t>
+          <t>11239; 24999</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18260; 34591</t>
+          <t>18118; 33690</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13730; 27978</t>
+          <t>13539; 28516</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36421; 58972</t>
+          <t>35959; 58277</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39149; 61221</t>
+          <t>38028; 59793</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44606; 69523</t>
+          <t>45231; 68959</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30793; 52133</t>
+          <t>30031; 51762</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>98898; 129850</t>
+          <t>98461; 130729</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96409; 127193</t>
+          <t>96632; 128679</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74365; 103934</t>
+          <t>73987; 105283</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83378; 192532</t>
+          <t>85095; 196712</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>84568; 112638</t>
+          <t>83875; 112949</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79135; 109947</t>
+          <t>79780; 109427</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78067; 107974</t>
+          <t>77560; 108202</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>85121; 138824</t>
+          <t>84499; 142608</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>190643; 232740</t>
+          <t>190555; 231108</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182712; 225701</t>
+          <t>182534; 225112</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160639; 202155</t>
+          <t>158663; 200926</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>181128; 298933</t>
+          <t>180719; 303305</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2003-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,63%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,53%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>17,87%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16,04%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,72; 23,74</t>
+          <t>10,28; 20,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 22,28</t>
+          <t>12,54; 23,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 17,73</t>
+          <t>5,86; 14,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 15,69</t>
+          <t>2,29; 30,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,34; 20,14</t>
+          <t>13,29; 24,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 23,88</t>
+          <t>10,84; 21,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 14,75</t>
+          <t>7,48; 17,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 36,15</t>
+          <t>6,4; 15,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,15; 20,18</t>
+          <t>12,78; 19,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 20,4</t>
+          <t>13,5; 21,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 14,24</t>
+          <t>7,66; 13,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 24,2</t>
+          <t>6,21; 19,95</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14,54%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>21,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>20,05%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>13,82%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,05; 26,69</t>
+          <t>11,8; 19,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,88; 24,95</t>
+          <t>10,63; 18,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 18,78</t>
+          <t>11,16; 18,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,59</t>
+          <t>10,36; 21,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,8; 19,6</t>
+          <t>17,45; 26,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 18,63</t>
+          <t>15,6; 25,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,89; 19,12</t>
+          <t>10,03; 18,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 22,14</t>
+          <t>6,28; 14,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,27; 21,57</t>
+          <t>15,51; 21,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,42; 19,92</t>
+          <t>13,82; 19,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,77; 17,31</t>
+          <t>11,74; 17,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,76; 16,72</t>
+          <t>9,38; 16,74</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>20,98%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14,26%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11,43%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33,67%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,58; 27,06</t>
+          <t>10,9; 20,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,33; 19,91</t>
+          <t>9,38; 18,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 16,35</t>
+          <t>9,34; 18,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,11; 57,23</t>
+          <t>12,98; 24,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 19,8</t>
+          <t>16,15; 26,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 18,11</t>
+          <t>10,25; 19,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 17,96</t>
+          <t>7,95; 16,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,22; 24,42</t>
+          <t>17,97; 30,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,35; 22,01</t>
+          <t>14,34; 21,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,95; 17,12</t>
+          <t>10,85; 17,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,49; 15,63</t>
+          <t>9,76; 15,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,35; 42,56</t>
+          <t>16,83; 25,5</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11,44%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15,93%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>15,99%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 15,52</t>
+          <t>8,77; 16,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,43; 20,46</t>
+          <t>5,89; 12,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 21,43</t>
+          <t>9,64; 17,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 16,89</t>
+          <t>7,76; 15,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 16,45</t>
+          <t>7,98; 15,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 12,74</t>
+          <t>11,96; 20,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 17,67</t>
+          <t>11,9; 21,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 16,03</t>
+          <t>8,61; 17,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 14,69</t>
+          <t>9,41; 14,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 15,34</t>
+          <t>9,6; 15,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,8; 18,0</t>
+          <t>11,6; 17,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 15,05</t>
+          <t>8,7; 14,85</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>17,57%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>16,78%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>13,51%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,26; 20,27</t>
+          <t>12,22; 16,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,41</t>
+          <t>11,29; 15,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,23; 15,99</t>
+          <t>11,05; 15,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,97; 29,98</t>
+          <t>11,22; 18,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 16,49</t>
+          <t>15,19; 19,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,34; 15,56</t>
+          <t>14,38; 19,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,44</t>
+          <t>11,24; 15,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,3; 19,08</t>
+          <t>11,91; 16,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,33; 17,38</t>
+          <t>14,28; 17,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,36; 16,48</t>
+          <t>13,3; 16,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,67; 14,78</t>
+          <t>11,75; 14,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 21,61</t>
+          <t>12,21; 16,31</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20989</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24946</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13252</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12725</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>23058</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>21365</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>14530</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11817</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20989</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24946</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13252</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27702</t>
+          <t>24858</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16405; 30620</t>
+          <t>14758; 29184</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15257; 29676</t>
+          <t>17819; 33684</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8825; 22106</t>
+          <t>8149; 19526</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7081; 18060</t>
+          <t>2813; 37163</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14845; 28909</t>
+          <t>17142; 31377</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17693; 33936</t>
+          <t>14435; 29206</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8235; 20524</t>
+          <t>9325; 22007</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3978; 49435</t>
+          <t>7637; 18750</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35844; 54991</t>
+          <t>34832; 53661</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36073; 56161</t>
+          <t>37171; 58448</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20453; 37567</t>
+          <t>20195; 36496</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14648; 60932</t>
+          <t>15032; 48323</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31474</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29790</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30912</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33817</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>38399</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>26707</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17615</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31474</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29790</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30912</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54779</t>
+          <t>51709</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31680; 49589</t>
+          <t>24177; 40236</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30421; 47779</t>
+          <t>22620; 38997</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20326; 36287</t>
+          <t>23517; 39706</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11667; 25403</t>
+          <t>24095; 50730</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24173; 40157</t>
+          <t>32419; 49982</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22332; 39644</t>
+          <t>29868; 48136</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22945; 40271</t>
+          <t>19387; 35130</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26129; 55171</t>
+          <t>11411; 26669</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59647; 84289</t>
+          <t>60600; 83475</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58277; 80550</t>
+          <t>55868; 80105</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47530; 69935</t>
+          <t>47408; 71067</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42569; 72914</t>
+          <t>38872; 69353</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>21053</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20624</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>21243</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29975</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>27425</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>20635</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>16937</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>63290</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>21053</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20624</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>21243</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32596</t>
+          <t>36965</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95885</t>
+          <t>66941</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20364; 35373</t>
+          <t>15188; 28290</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14937; 28795</t>
+          <t>14287; 28469</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11781; 24220</t>
+          <t>14983; 29503</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37811; 107582</t>
+          <t>21701; 41519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15278; 27589</t>
+          <t>21110; 35139</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14332; 27588</t>
+          <t>14828; 27780</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14412; 28819</t>
+          <t>11784; 23969</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24291; 44859</t>
+          <t>27789; 46904</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38746; 59451</t>
+          <t>38734; 57994</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32529; 50846</t>
+          <t>32213; 50947</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29276; 48248</t>
+          <t>30118; 49000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68217; 158177</t>
+          <t>54169; 82079</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24019</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17437</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18393</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>22822</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>30832</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>30781</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20326</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24019</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17437</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>38983</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15851; 30957</t>
+          <t>17295; 32484</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22119; 39607</t>
+          <t>11552; 25264</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23337; 41244</t>
+          <t>18378; 33981</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13519; 28065</t>
+          <t>12925; 25853</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16454; 32431</t>
+          <t>15919; 31644</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11239; 24999</t>
+          <t>23156; 40475</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18118; 33690</t>
+          <t>22898; 40883</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13539; 28516</t>
+          <t>14219; 28881</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35959; 58277</t>
+          <t>37345; 59068</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38028; 59793</t>
+          <t>37405; 60289</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45231; 68959</t>
+          <t>44457; 68556</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30031; 51762</t>
+          <t>28861; 49270</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>120</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>94910</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>113305</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>111231</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>88955</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>113048</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97535</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92797</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90901</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>105364</t>
+          <t>87580</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>218412</t>
+          <t>182490</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>98461; 130729</t>
+          <t>83687; 111819</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96632; 128679</t>
+          <t>79432; 108594</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73987; 105283</t>
+          <t>77447; 106142</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85095; 196712</t>
+          <t>77347; 124939</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>83875; 112949</t>
+          <t>97996; 128552</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79780; 109427</t>
+          <t>95300; 127320</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77560; 108202</t>
+          <t>73998; 103586</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>84499; 142608</t>
+          <t>73954; 103379</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>190555; 231108</t>
+          <t>189962; 232012</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182534; 225112</t>
+          <t>181667; 225261</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158663; 200926</t>
+          <t>159691; 201619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>180719; 303305</t>
+          <t>159899; 213725</t>
         </is>
       </c>
     </row>
